--- a/docs/downloads/09/t8_transition_marovoay_tous.xlsx
+++ b/docs/downloads/09/t8_transition_marovoay_tous.xlsx
@@ -512,12 +512,6 @@
           <t>Tubercule+Céréale</t>
         </is>
       </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,12 +529,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -627,12 +615,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -650,12 +632,6 @@
           <t>Rien</t>
         </is>
       </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -788,12 +764,6 @@
           <t>Rien</t>
         </is>
       </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -880,12 +850,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -902,12 +866,6 @@
         <is>
           <t>Patate douce</t>
         </is>
-      </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24">
-        <v>3.5</v>
       </c>
     </row>
     <row r="25">

--- a/docs/downloads/09/t8_transition_marovoay_tous.xlsx
+++ b/docs/downloads/09/t8_transition_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -940,7 +940,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
